--- a/artfynd/A 27981-2022 artfynd.xlsx
+++ b/artfynd/A 27981-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27981-2022 artfynd.xlsx
+++ b/artfynd/A 27981-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66334181</v>
+        <v>113987344</v>
       </c>
       <c r="B2" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224416</v>
+        <v>220164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Måltorp 500 m O, Ög</t>
+          <t>49 Ärlången, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547366.6312869923</v>
+        <v>547376</v>
       </c>
       <c r="R2" t="n">
-        <v>6465499.736944588</v>
+        <v>6465425</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Ström</t>
+          <t>Per Toräng</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Adb inventering gräsmarker</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>66334184</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547366.6312869923</v>
+        <v>547367</v>
       </c>
       <c r="R3" t="n">
-        <v>6465499.736944588</v>
+        <v>6465500</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +847,9 @@
           <t>2017-06-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +873,405 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113986972</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>49 Ärlången, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547376</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6465425</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Adb inventering gräsmarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113986188</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>49 Ärlången, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547376</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6465425</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Adb inventering gräsmarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113983322</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>49 Ärlången, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547376</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6465425</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Adb inventering gräsmarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>66334181</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Måltorp 500 m O, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547367</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6465500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Ström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27981-2022 artfynd.xlsx
+++ b/artfynd/A 27981-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Adb inventering gräsmarker</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113987344</t>
         </is>
       </c>
     </row>
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66334184</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
           <t>Adb inventering gräsmarker</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113986972</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
           <t>Adb inventering gräsmarker</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113986188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Adb inventering gräsmarker</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113983322</t>
         </is>
       </c>
     </row>
@@ -1272,8 +1302,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66334181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>